--- a/business_surveys/001_chemical_compound_selection_survey--business_surveys.xlsx
+++ b/business_surveys/001_chemical_compound_selection_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -839,8 +839,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -868,12 +868,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'organic',_'value':_'organic'}</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Organic', 'value': 'organic'}</t>
+          <t>Organic</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'inorganic',_'value':_'inorganic'}</t>
+          <t>inorganic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Inorganic', 'value': 'inorganic'}</t>
+          <t>Inorganic</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'organometallic',_'value':_'organometallic'}</t>
+          <t>organometallic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Organometallic', 'value': 'organometallic'}</t>
+          <t>Organometallic</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'polymer',_'value':_'polymer'}</t>
+          <t>polymer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Polymer', 'value': 'polymer'}</t>
+          <t>Polymer</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'high_solubility',_'value':_'solubility'}</t>
+          <t>high_solubility</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'High Solubility', 'value': 'solubility'}</t>
+          <t>High Solubility</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'thermal_stability',_'value':_'stability'}</t>
+          <t>thermal_stability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Thermal Stability', 'value': 'stability'}</t>
+          <t>Thermal Stability</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'low_reactivity',_'value':_'reactivity'}</t>
+          <t>low_reactivity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Low Reactivity', 'value': 'reactivity'}</t>
+          <t>Low Reactivity</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'optical_clarity',_'value':_'clarity'}</t>
+          <t>optical_clarity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Optical Clarity', 'value': 'clarity'}</t>
+          <t>Optical Clarity</t>
         </is>
       </c>
     </row>
